--- a/SGC-CKN/Excel/fc55ff55-331c-4d93-a2d7-0358a48ece5f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-10_D800_15-03-2026.xlsx
+++ b/SGC-CKN/Excel/fc55ff55-331c-4d93-a2d7-0358a48ece5f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-10_D800_15-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-10</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>KL-002</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>KCL-0002</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">16:58
@@ -184,7 +184,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">21:17
@@ -198,7 +198,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">21:48
@@ -212,7 +212,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, TT chặt đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23:13

--- a/SGC-CKN/Excel/fc55ff55-331c-4d93-a2d7-0358a48ece5f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-10_D800_15-03-2026.xlsx
+++ b/SGC-CKN/Excel/fc55ff55-331c-4d93-a2d7-0358a48ece5f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-10_D800_15-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="70">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>KCL-0002</t>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">15:30
@@ -106,9 +106,6 @@
 15/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">17:00
 15/03/2026</t>
   </si>
@@ -150,7 +144,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">19:25
@@ -160,9 +154,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">20:21
 15/03/2026</t>
   </si>
@@ -170,7 +161,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sét xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20:22
@@ -196,9 +187,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">21:48
@@ -257,7 +245,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -333,11 +321,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -350,7 +333,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,12 +392,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFED7AA"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFFED7AA"/>
       </patternFill>
     </fill>
     <fill>
@@ -425,11 +408,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -525,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -596,17 +574,17 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -626,22 +604,13 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1242,24 +1211,24 @@
         <v>5.04</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-6.98</v>
@@ -1277,24 +1246,24 @@
         <v>11.08</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="12">
         <v>-9.38</v>
@@ -1312,24 +1281,24 @@
         <v>6.93</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="F14" s="15">
         <v>-17.58</v>
@@ -1347,24 +1316,24 @@
         <v>10.42</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="18">
         <v>-21.92</v>
@@ -1382,198 +1351,198 @@
         <v>5.25</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="21" t="s">
+      <c r="A16" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="21">
+      <c r="F16" s="18">
         <v>-26.12</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="18">
         <v>-36.32</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="18">
         <v>0.93</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="18">
         <v>10.2</v>
       </c>
       <c r="J16" s="8">
         <v>10.93</v>
       </c>
-      <c r="K16" s="22" t="s">
-        <v>30</v>
+      <c r="K16" s="19" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="F17" s="21">
+        <v>-36.32</v>
+      </c>
+      <c r="G17" s="21">
+        <v>-38.32</v>
+      </c>
+      <c r="H17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="I17" s="21">
+        <v>2</v>
+      </c>
+      <c r="J17" s="24">
+        <v>2.22</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="26" t="s">
+      <c r="C18" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="D18" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="24">
-        <v>-36.32</v>
-      </c>
-      <c r="G17" s="24">
+      <c r="E18" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="25">
         <v>-38.32</v>
       </c>
-      <c r="H17" s="24">
-        <v>0.9</v>
-      </c>
-      <c r="I17" s="24">
+      <c r="G18" s="25">
+        <v>-40.32</v>
+      </c>
+      <c r="H18" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="25">
         <v>2</v>
       </c>
-      <c r="J17" s="27">
-        <v>2.22</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="J18" s="24">
+        <v>4</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="30" t="s">
+      <c r="C19" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E19" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="28">
-        <v>-38.32</v>
-      </c>
-      <c r="G18" s="28">
+      <c r="F19" s="28">
         <v>-40.32</v>
       </c>
-      <c r="H18" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="I18" s="28">
-        <v>2</v>
-      </c>
-      <c r="J18" s="27">
-        <v>4</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="G19" s="28">
+        <v>-44.22</v>
+      </c>
+      <c r="H19" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="I19" s="28">
+        <v>3.9</v>
+      </c>
+      <c r="J19" s="24">
+        <v>2.79</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B20" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C20" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D20" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E20" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="31">
-        <v>-40.32</v>
-      </c>
-      <c r="G19" s="31">
+      <c r="F20" s="31">
         <v>-44.22</v>
       </c>
-      <c r="H19" s="31">
-        <v>1.4</v>
-      </c>
-      <c r="I19" s="31">
-        <v>3.9</v>
-      </c>
-      <c r="J19" s="27">
-        <v>2.79</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
+      <c r="G20" s="31">
+        <v>-44.85</v>
+      </c>
+      <c r="H20" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="I20" s="31">
+        <v>0.63</v>
+      </c>
+      <c r="J20" s="24">
+        <v>3.15</v>
+      </c>
+      <c r="K20" s="32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="34">
-        <v>-44.22</v>
-      </c>
-      <c r="G20" s="34">
-        <v>-44.85</v>
-      </c>
-      <c r="H20" s="34">
-        <v>0.2</v>
-      </c>
-      <c r="I20" s="34">
-        <v>0.63</v>
-      </c>
-      <c r="J20" s="27">
-        <v>3.15</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1655,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1668,31 +1637,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1732,7 +1701,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1761,7 +1730,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1790,7 +1759,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1819,25 +1788,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D6" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="18">
         <v>-21.92</v>
       </c>
       <c r="F6" s="18">
-        <v>-26.12</v>
+        <v>-36.32</v>
       </c>
       <c r="G6" s="18">
-        <v>0.8</v>
+        <v>1.73</v>
       </c>
       <c r="H6" s="18">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="I6" s="8">
-        <v>5.25</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1854,48 +1823,48 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-26.12</v>
+        <v>-36.32</v>
       </c>
       <c r="F7" s="21">
-        <v>-36.32</v>
+        <v>-38.32</v>
       </c>
       <c r="G7" s="21">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="21">
-        <v>10.2</v>
-      </c>
-      <c r="I7" s="8">
-        <v>10.93</v>
+        <v>2</v>
+      </c>
+      <c r="I7" s="24">
+        <v>2.22</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="24">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="24">
+      <c r="C8" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="24">
-        <v>-36.32</v>
-      </c>
-      <c r="F8" s="24">
+      <c r="E8" s="25">
         <v>-38.32</v>
       </c>
-      <c r="G8" s="24">
-        <v>0.9</v>
-      </c>
-      <c r="H8" s="24">
+      <c r="F8" s="25">
+        <v>-40.32</v>
+      </c>
+      <c r="G8" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="25">
         <v>2</v>
       </c>
-      <c r="I8" s="27">
-        <v>2.22</v>
+      <c r="I8" s="24">
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1906,25 +1875,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.32</v>
+        <v>-40.32</v>
       </c>
       <c r="F9" s="28">
-        <v>-40.32</v>
+        <v>-44.22</v>
       </c>
       <c r="G9" s="28">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="H9" s="28">
-        <v>2</v>
-      </c>
-      <c r="I9" s="27">
-        <v>4</v>
+        <v>3.9</v>
+      </c>
+      <c r="I9" s="24">
+        <v>2.79</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1941,76 +1910,47 @@
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-40.32</v>
+        <v>-44.22</v>
       </c>
       <c r="F10" s="31">
-        <v>-44.22</v>
+        <v>-44.85</v>
       </c>
       <c r="G10" s="31">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="31">
-        <v>3.9</v>
-      </c>
-      <c r="I10" s="27">
-        <v>2.79</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+        <v>0.63</v>
+      </c>
+      <c r="I10" s="24">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="36">
         <v>10</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-44.22</v>
-      </c>
-      <c r="F11" s="34">
+      <c r="E11" s="36">
+        <v>-0.68</v>
+      </c>
+      <c r="F11" s="36">
         <v>-44.85</v>
       </c>
-      <c r="G11" s="34">
-        <v>0.2</v>
-      </c>
-      <c r="H11" s="34">
-        <v>0.63</v>
-      </c>
-      <c r="I11" s="27">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="39">
-        <v>10</v>
-      </c>
-      <c r="E12" s="39">
-        <v>-0.68</v>
-      </c>
-      <c r="F12" s="39">
-        <v>-44.85</v>
-      </c>
-      <c r="G12" s="39">
+      <c r="G11" s="36">
         <v>7.8</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H11" s="36">
         <v>44.17</v>
       </c>
-      <c r="I12" s="39">
+      <c r="I11" s="36">
         <v>5.66</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/fc55ff55-331c-4d93-a2d7-0358a48ece5f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-10_D800_15-03-2026.xlsx
+++ b/SGC-CKN/Excel/fc55ff55-331c-4d93-a2d7-0358a48ece5f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-10_D800_15-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="71">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -104,6 +104,9 @@
   <si>
     <t xml:space="preserve">16:45
 15/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -1211,24 +1214,24 @@
         <v>5.04</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-6.98</v>
@@ -1246,12 +1249,12 @@
         <v>11.08</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
@@ -1260,10 +1263,10 @@
         <v>27</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-9.38</v>
@@ -1281,24 +1284,24 @@
         <v>6.93</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="15">
         <v>-17.58</v>
@@ -1316,24 +1319,24 @@
         <v>10.42</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="18">
         <v>-21.92</v>
@@ -1351,24 +1354,24 @@
         <v>5.25</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="18">
         <v>-26.12</v>
@@ -1386,24 +1389,24 @@
         <v>10.93</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="21">
         <v>-36.32</v>
@@ -1421,24 +1424,24 @@
         <v>2.22</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="25">
         <v>-38.32</v>
@@ -1456,24 +1459,24 @@
         <v>4</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="28">
         <v>-40.32</v>
@@ -1491,24 +1494,24 @@
         <v>2.79</v>
       </c>
       <c r="K19" s="29" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="31">
         <v>-44.22</v>
@@ -1526,12 +1529,12 @@
         <v>3.15</v>
       </c>
       <c r="K20" s="32" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -1637,31 +1640,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1701,7 +1704,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1759,7 +1762,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1788,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="18">
         <v>2</v>
@@ -1817,7 +1820,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="21">
         <v>1</v>
@@ -1846,7 +1849,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1875,7 +1878,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1904,7 +1907,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1927,13 +1930,13 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D11" s="36">
         <v>10</v>

--- a/SGC-CKN/Excel/fc55ff55-331c-4d93-a2d7-0358a48ece5f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-10_D800_15-03-2026.xlsx
+++ b/SGC-CKN/Excel/fc55ff55-331c-4d93-a2d7-0358a48ece5f_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-10_D800_15-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi đại trà_lô đất ký hiệu CT-02</t>
+    <t>Thi công cọc khoan nhồi, tường vây cho các hạng mục_Lô CT-02</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>SGC-KCN0001</t>
+    <t>SGC-KCN0002</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -150,7 +150,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">19:25
+    <t xml:space="preserve">19:23
 15/03/2026</t>
   </si>
   <si>
@@ -1345,13 +1345,13 @@
         <v>-26.12</v>
       </c>
       <c r="H15" s="18">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="I15" s="18">
         <v>4.2</v>
       </c>
       <c r="J15" s="8">
-        <v>5.25</v>
+        <v>5.48</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1380,13 +1380,13 @@
         <v>-36.32</v>
       </c>
       <c r="H16" s="18">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="I16" s="18">
         <v>10.2</v>
       </c>
       <c r="J16" s="8">
-        <v>10.93</v>
+        <v>10.55</v>
       </c>
       <c r="K16" s="19" t="s">
         <v>30</v>
